--- a/diseases/d011/1995-1999.xlsx
+++ b/diseases/d011/1995-1999.xlsx
@@ -10523,6 +10523,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11448,6 +11453,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11983,6 +11993,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12518,6 +12533,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13053,6 +13073,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13588,6 +13613,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14123,6 +14153,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14658,6 +14693,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15193,6 +15233,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15728,6 +15773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16263,6 +16313,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16798,6 +16853,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17333,6 +17393,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18258,6 +18323,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18793,6 +18863,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19328,6 +19403,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19863,6 +19943,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20398,6 +20483,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20933,6 +21023,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21468,6 +21563,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22003,6 +22103,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22538,6 +22643,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23073,6 +23183,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23608,6 +23723,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24143,6 +24263,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25068,6 +25193,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25603,6 +25733,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26138,6 +26273,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26673,6 +26813,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27208,6 +27353,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27743,6 +27893,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28278,6 +28433,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28813,6 +28973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29348,6 +29513,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29883,6 +30053,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30416,6 +30591,11 @@
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">

--- a/diseases/d011/1995-1999.xlsx
+++ b/diseases/d011/1995-1999.xlsx
@@ -10518,6 +10518,11 @@
       <c r="Q52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10530,12 +10535,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -11433,6 +11448,11 @@
       <c r="Q57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11445,12 +11465,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -11958,6 +11988,11 @@
       <c r="Q60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11970,12 +12005,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -12483,6 +12528,11 @@
       <c r="Q63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12495,12 +12545,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -13008,6 +13068,11 @@
       <c r="Q66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13020,12 +13085,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -13533,6 +13608,11 @@
       <c r="Q69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13545,12 +13625,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -14058,6 +14148,11 @@
       <c r="Q72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14070,12 +14165,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -14583,6 +14688,11 @@
       <c r="Q75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14595,12 +14705,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -15108,6 +15228,11 @@
       <c r="Q78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15120,12 +15245,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -15633,6 +15768,11 @@
       <c r="Q81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15645,12 +15785,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -16158,6 +16308,11 @@
       <c r="Q84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16170,12 +16325,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -16683,6 +16848,11 @@
       <c r="Q87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16695,12 +16865,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -17208,6 +17388,11 @@
       <c r="Q90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17220,12 +17405,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -18123,6 +18318,11 @@
       <c r="Q95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18135,12 +18335,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -18648,6 +18858,11 @@
       <c r="Q98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18660,12 +18875,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -19173,6 +19398,11 @@
       <c r="Q101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19185,12 +19415,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -19698,6 +19938,11 @@
       <c r="Q104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19710,12 +19955,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -20223,6 +20478,11 @@
       <c r="Q107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20235,12 +20495,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -20748,6 +21018,11 @@
       <c r="Q110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20760,12 +21035,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -21273,6 +21558,11 @@
       <c r="Q113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21285,12 +21575,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -21798,6 +22098,11 @@
       <c r="Q116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21810,12 +22115,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -22323,6 +22638,11 @@
       <c r="Q119" t="n">
         <v>0</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22335,12 +22655,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -22848,6 +23178,11 @@
       <c r="Q122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22860,12 +23195,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -23373,6 +23718,11 @@
       <c r="Q125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23385,12 +23735,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -23898,6 +24258,11 @@
       <c r="Q128" t="n">
         <v>0</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23910,12 +24275,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -24813,6 +25188,11 @@
       <c r="Q133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24825,12 +25205,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -25338,6 +25728,11 @@
       <c r="Q136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25350,12 +25745,22 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -25863,6 +26268,11 @@
       <c r="Q139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25875,12 +26285,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -26388,6 +26808,11 @@
       <c r="Q142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26400,12 +26825,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -26913,6 +27348,11 @@
       <c r="Q145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26925,12 +27365,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -27438,6 +27888,11 @@
       <c r="Q148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27450,12 +27905,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -27963,6 +28428,11 @@
       <c r="Q151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27975,12 +28445,22 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -28488,6 +28968,11 @@
       <c r="Q154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28500,12 +28985,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -29013,6 +29508,11 @@
       <c r="Q157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29025,12 +29525,22 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -29538,6 +30048,11 @@
       <c r="Q160" t="n">
         <v>0</v>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29550,12 +30065,22 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -30063,6 +30588,11 @@
       <c r="Q163" t="n">
         <v>0</v>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30075,12 +30605,22 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
